--- a/vrn_processing/capacity_vehicles.xlsx
+++ b/vrn_processing/capacity_vehicles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,168 +443,552 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CG07CL7712</t>
+          <t>UP75AT1776</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>40.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CG10G1465</t>
+          <t>MP44ZB9901</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>41.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CG15EA2204</t>
+          <t>UP32MN8719</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>41.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CG10AX0652</t>
+          <t>UP78DN3366</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>30.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CG25H6030</t>
+          <t>UP78DN3663</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CG15EC9360</t>
+          <t>UP78HT8051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>52.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JH02BU0968</t>
+          <t>UP78HT4081</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>52.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CG10BX3882</t>
+          <t>BR02PB8738</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>60.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CG08AY5400</t>
+          <t>UP66T9870</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>42.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MP13ZF8113</t>
+          <t>UP78JT7048</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>53.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OD05T3787</t>
+          <t>UP78JT4148</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>53.0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CG04PT3339</t>
+          <t>AR01U0551</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CG07CG9555</t>
+          <t>WB39B3052</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JH19C6277</t>
+          <t>BR28P3405</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UP30BT7736</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UP15GT4454</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UP15ET9169</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NL01B3488</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UP81CT4669</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UP22AT1411</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BR06PG6629</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UK07PA4475</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MP09AG1352</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MP44ZE6257</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BR45P2121</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UP63AT9646</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UP53GT3425</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>UP81DT2754</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RJ18PB3575</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NL07B3111</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UP51AT2236</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UP15ET9658</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UP32MN8148</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BR02PC5088</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UP30BT5718</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BR02PC4188</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BR02PC4288</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BR06PG5563</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UP15ET6976</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UP31AT9457</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>UP15GT3946</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UP30BT0858</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UP30AT0320</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NL07B0577</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>UP61AT7935</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NL02B3611</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>39.0</t>
         </is>
       </c>
     </row>
